--- a/artfynd/A 40116-2025 artfynd.xlsx
+++ b/artfynd/A 40116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735591</v>
       </c>
       <c r="B2" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40116-2025 artfynd.xlsx
+++ b/artfynd/A 40116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735591</v>
       </c>
       <c r="B2" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40116-2025 artfynd.xlsx
+++ b/artfynd/A 40116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128340066</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ängesån, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>828871</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7422251</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40116-2025 artfynd.xlsx
+++ b/artfynd/A 40116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735591</v>
       </c>
       <c r="B2" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340066</v>
       </c>
       <c r="B3" t="n">
-        <v>80135</v>
+        <v>80136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40116-2025 artfynd.xlsx
+++ b/artfynd/A 40116-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735591</v>
       </c>
       <c r="B2" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340066</v>
       </c>
       <c r="B3" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40116-2025 artfynd.xlsx
+++ b/artfynd/A 40116-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128340066</v>
       </c>
       <c r="B3" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40116-2025 artfynd.xlsx
+++ b/artfynd/A 40116-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128340066</v>
       </c>
       <c r="B3" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40116-2025 artfynd.xlsx
+++ b/artfynd/A 40116-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128340066</v>
       </c>
       <c r="B3" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40116-2025 artfynd.xlsx
+++ b/artfynd/A 40116-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128340066</v>
       </c>
       <c r="B3" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40116-2025 artfynd.xlsx
+++ b/artfynd/A 40116-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128340066</v>
       </c>
       <c r="B3" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40116-2025 artfynd.xlsx
+++ b/artfynd/A 40116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127735591</v>
       </c>
       <c r="B2" t="n">
-        <v>80189</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128340066</v>
+        <v>128340064</v>
       </c>
       <c r="B3" t="n">
-        <v>80230</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>828871</v>
+        <v>829133</v>
       </c>
       <c r="R3" t="n">
-        <v>7422251</v>
+        <v>7422043</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,6 +884,324 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128340066</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ängesån, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>828871</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7422251</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127735585</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ängesån, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>829133</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7422041</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128340065</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ängesån, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>829133</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7422042</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40116-2025 artfynd.xlsx
+++ b/artfynd/A 40116-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735591</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340064</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340066</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735585</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340065</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>